--- a/test/input/scenarios/mobi50test/scoringParametersIT.xlsx
+++ b/test/input/scenarios/mobi50test/scoringParametersIT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11027"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\devsbb\code\matsim-sbb\test\input\scenarios\mobi31test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annevaleriepreto/Documents/EPFL/matsim-sbb/test/input/scenarios/mobi50test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353E7CA8-9F37-48F2-948B-DA9186C94F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BCDBFA-4C7D-6845-94DC-91F300C98923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="25170" windowHeight="15720" tabRatio="674" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="900" windowWidth="29080" windowHeight="18060" tabRatio="674" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScoringParams" sheetId="25" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="71">
   <si>
     <t>adaptation time</t>
   </si>
@@ -238,6 +238,18 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>rail</t>
+  </si>
+  <si>
+    <t>tram</t>
+  </si>
+  <si>
+    <t>bus</t>
+  </si>
+  <si>
+    <t>other</t>
   </si>
 </sst>
 </file>
@@ -598,17 +610,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -655,113 +665,109 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -774,13 +780,13 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -792,28 +798,22 @@
     <xf numFmtId="2" fontId="1" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="3" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="16" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -834,7 +834,7 @@
     <xf numFmtId="0" fontId="16" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -864,7 +864,7 @@
     <xf numFmtId="164" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -885,7 +885,7 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -906,26 +906,16 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="169" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -937,17 +927,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="6">
     <dxf>
       <font>
         <color theme="0" tint="-0.14996795556505021"/>
@@ -957,16 +947,6 @@
       <font>
         <color theme="0" tint="-0.14996795556505021"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEAEAEA"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1003,37 +983,6 @@
           <bgColor rgb="FFEAEAEA"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="7" tint="-0.749961851863155"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.14996795556505021"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEAEAEA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <color theme="7" tint="-0.749961851863155"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1403,863 +1352,1097 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB22"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:X22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
-    <col min="4" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" customWidth="1"/>
-    <col min="14" max="14" width="10.140625" customWidth="1"/>
-    <col min="15" max="15" width="5.5703125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="33.7109375" customWidth="1"/>
-    <col min="19" max="19" width="24.5703125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.42578125" style="2" customWidth="1"/>
-    <col min="22" max="24" width="7.85546875" style="1" customWidth="1"/>
-    <col min="25" max="25" width="7.28515625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="7.85546875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.85546875" style="1" customWidth="1"/>
-    <col min="29" max="30" width="7.85546875" customWidth="1"/>
-    <col min="31" max="31" width="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+    <col min="7" max="11" width="11.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" customWidth="1"/>
+    <col min="13" max="16" width="12.5" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" customWidth="1"/>
+    <col min="18" max="18" width="10.1640625" customWidth="1"/>
+    <col min="19" max="19" width="5.5" style="2" customWidth="1"/>
+    <col min="20" max="20" width="33.6640625" customWidth="1"/>
+    <col min="23" max="23" width="24.5" style="1" customWidth="1"/>
+    <col min="24" max="24" width="8.5" style="1" customWidth="1"/>
+    <col min="26" max="28" width="7.83203125" customWidth="1"/>
+    <col min="29" max="29" width="7.33203125" customWidth="1"/>
+    <col min="30" max="30" width="7.83203125" customWidth="1"/>
+    <col min="31" max="31" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="7.83203125" customWidth="1"/>
+    <col min="35" max="35" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:20" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="134" t="s">
+      <c r="B1" s="122" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="7"/>
-    </row>
-    <row r="2" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="5"/>
+    </row>
+    <row r="2" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G2" s="133" t="s">
+      <c r="G2" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="I2" s="121" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="121" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="121" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="M2" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="N2" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="O2" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="P2" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="Q2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="R2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="13"/>
-    </row>
-    <row r="3" spans="1:16" ht="50.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="115" t="s">
+      <c r="S2" s="11"/>
+    </row>
+    <row r="3" spans="1:20" ht="50.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="17"/>
+      <c r="B3" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="108" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="123" t="s">
+      <c r="D3" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="124" t="s">
+      <c r="E3" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="124" t="s">
+      <c r="F3" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="G3" s="123" t="s">
+      <c r="G3" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="123" t="s">
+      <c r="H3" s="115" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="115" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="115" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="115" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="124" t="s">
+      <c r="M3" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="124" t="s">
+      <c r="N3" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="124" t="s">
+      <c r="O3" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="116" t="s">
+      <c r="P3" s="108" t="s">
         <v>62</v>
       </c>
-      <c r="M3" s="123" t="s">
+      <c r="Q3" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="N3" s="116" t="s">
+      <c r="R3" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="20" t="s">
+      <c r="S3" s="11"/>
+      <c r="T3" s="18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="117" t="s">
+      <c r="B4" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="118"/>
-      <c r="D4" s="92">
+      <c r="C4" s="110"/>
+      <c r="D4" s="84">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="E4" s="93">
+      <c r="E4" s="85">
         <v>-0.7</v>
       </c>
-      <c r="F4" s="125">
-        <v>0</v>
-      </c>
-      <c r="G4" s="92">
+      <c r="F4" s="85">
+        <v>0</v>
+      </c>
+      <c r="G4" s="84">
         <v>-0.02</v>
       </c>
-      <c r="H4" s="92">
-        <v>0</v>
-      </c>
-      <c r="I4" s="132">
+      <c r="H4" s="84">
+        <v>-0.02</v>
+      </c>
+      <c r="I4" s="84">
+        <v>-0.02</v>
+      </c>
+      <c r="J4" s="84">
+        <v>-0.02</v>
+      </c>
+      <c r="K4" s="84">
+        <v>-0.02</v>
+      </c>
+      <c r="L4" s="84">
+        <v>0</v>
+      </c>
+      <c r="M4" s="120">
         <v>-0.43</v>
       </c>
-      <c r="J4" s="93">
+      <c r="N4" s="85">
         <v>-0.26</v>
       </c>
-      <c r="K4" s="93">
+      <c r="O4" s="85">
         <v>-0.06</v>
       </c>
-      <c r="L4" s="129">
+      <c r="P4" s="86">
         <v>-0.17</v>
       </c>
-      <c r="M4" s="92">
+      <c r="Q4" s="84">
         <v>0.02</v>
       </c>
-      <c r="N4" s="94">
+      <c r="R4" s="86">
         <v>-0.24</v>
       </c>
-      <c r="O4" s="14"/>
-      <c r="P4" s="21" t="s">
+      <c r="S4" s="12"/>
+      <c r="T4" s="19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:16" s="4" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:20" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="119" t="s">
+      <c r="B5" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="120"/>
-      <c r="D5" s="89">
-        <v>0</v>
-      </c>
-      <c r="E5" s="90">
-        <v>0</v>
-      </c>
-      <c r="F5" s="131">
-        <v>0</v>
-      </c>
-      <c r="G5" s="89">
-        <v>0</v>
-      </c>
-      <c r="H5" s="89">
-        <v>0</v>
-      </c>
-      <c r="I5" s="90">
-        <v>0</v>
-      </c>
-      <c r="J5" s="90">
-        <v>0</v>
-      </c>
-      <c r="K5" s="90">
-        <v>0</v>
-      </c>
-      <c r="L5" s="91">
-        <v>0</v>
-      </c>
-      <c r="M5" s="89">
-        <v>0</v>
-      </c>
-      <c r="N5" s="90">
-        <v>0</v>
-      </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="22" t="s">
+      <c r="C5" s="112"/>
+      <c r="D5" s="81">
+        <v>0</v>
+      </c>
+      <c r="E5" s="82">
+        <v>0</v>
+      </c>
+      <c r="F5" s="119">
+        <v>0</v>
+      </c>
+      <c r="G5" s="81">
+        <v>0</v>
+      </c>
+      <c r="H5" s="81">
+        <v>0</v>
+      </c>
+      <c r="I5" s="81">
+        <v>0</v>
+      </c>
+      <c r="J5" s="81">
+        <v>0</v>
+      </c>
+      <c r="K5" s="81">
+        <v>0</v>
+      </c>
+      <c r="L5" s="81">
+        <v>0</v>
+      </c>
+      <c r="M5" s="82">
+        <v>0</v>
+      </c>
+      <c r="N5" s="82">
+        <v>0</v>
+      </c>
+      <c r="O5" s="82">
+        <v>0</v>
+      </c>
+      <c r="P5" s="83">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="81">
+        <v>0</v>
+      </c>
+      <c r="R5" s="82">
+        <v>0</v>
+      </c>
+      <c r="S5" s="12"/>
+      <c r="T5" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="119" t="s">
+      <c r="B6" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="52">
+      <c r="C6" s="110"/>
+      <c r="D6" s="47">
         <v>-0.44</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="48">
         <v>-0.79</v>
       </c>
-      <c r="F6" s="87">
+      <c r="F6" s="48">
         <v>-0.17</v>
       </c>
-      <c r="G6" s="52">
+      <c r="G6" s="47">
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="47">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="I6" s="47">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="J6" s="47">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="K6" s="47">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="L6" s="47">
         <v>-0.31</v>
       </c>
-      <c r="I6" s="53">
+      <c r="M6" s="48">
         <v>-0.22</v>
       </c>
-      <c r="J6" s="53">
+      <c r="N6" s="48">
         <v>-0.09</v>
       </c>
-      <c r="K6" s="53">
+      <c r="O6" s="48">
         <v>-0.57999999999999996</v>
       </c>
-      <c r="L6" s="86">
+      <c r="P6" s="80">
         <v>-3.25</v>
       </c>
-      <c r="M6" s="52">
+      <c r="Q6" s="47">
         <v>-0.05</v>
       </c>
-      <c r="N6" s="53">
+      <c r="R6" s="48">
         <v>-0.7</v>
       </c>
-      <c r="O6" s="15"/>
-      <c r="P6" s="69" t="s">
+      <c r="S6" s="13"/>
+      <c r="T6" s="63" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="119" t="s">
+      <c r="B7" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="118"/>
-      <c r="D7" s="89">
-        <v>0</v>
-      </c>
-      <c r="E7" s="90">
-        <v>0</v>
-      </c>
-      <c r="F7" s="126">
-        <v>0</v>
-      </c>
-      <c r="G7" s="89">
-        <v>0</v>
-      </c>
-      <c r="H7" s="89">
-        <v>0</v>
-      </c>
-      <c r="I7" s="90">
-        <v>0</v>
-      </c>
-      <c r="J7" s="90">
-        <v>0</v>
-      </c>
-      <c r="K7" s="90">
-        <v>0</v>
-      </c>
-      <c r="L7" s="91">
-        <v>0</v>
-      </c>
-      <c r="M7" s="89">
-        <v>0</v>
-      </c>
-      <c r="N7" s="90">
-        <v>0</v>
-      </c>
-      <c r="O7" s="13"/>
-      <c r="P7" s="136" t="s">
+      <c r="C7" s="110"/>
+      <c r="D7" s="81">
+        <v>0</v>
+      </c>
+      <c r="E7" s="82">
+        <v>0</v>
+      </c>
+      <c r="F7" s="117">
+        <v>0</v>
+      </c>
+      <c r="G7" s="81">
+        <v>0</v>
+      </c>
+      <c r="H7" s="81">
+        <v>0</v>
+      </c>
+      <c r="I7" s="81">
+        <v>0</v>
+      </c>
+      <c r="J7" s="81">
+        <v>0</v>
+      </c>
+      <c r="K7" s="81">
+        <v>0</v>
+      </c>
+      <c r="L7" s="81">
+        <v>0</v>
+      </c>
+      <c r="M7" s="82">
+        <v>0</v>
+      </c>
+      <c r="N7" s="82">
+        <v>0</v>
+      </c>
+      <c r="O7" s="82">
+        <v>0</v>
+      </c>
+      <c r="P7" s="83">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="81">
+        <v>0</v>
+      </c>
+      <c r="R7" s="82">
+        <v>0</v>
+      </c>
+      <c r="S7" s="11"/>
+      <c r="T7" s="124" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="16"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="88" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="K8" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="L8" s="130" t="s">
-        <v>66</v>
-      </c>
-      <c r="M8" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="N8" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="O8" s="13"/>
-      <c r="P8" s="136"/>
-    </row>
-    <row r="9" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
+    <row r="8" spans="1:20" ht="0.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="14"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="P8" s="118" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q8" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="R8" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="S8" s="11"/>
+      <c r="T8" s="124"/>
+    </row>
+    <row r="9" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="117" t="s">
+      <c r="B9" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="80">
+      <c r="C9" s="74">
         <v>-0.04</v>
       </c>
-      <c r="D9" s="95"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="97" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="96" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="96" t="s">
-        <v>66</v>
-      </c>
-      <c r="K9" s="96" t="s">
-        <v>66</v>
-      </c>
-      <c r="L9" s="99" t="s">
-        <v>66</v>
-      </c>
-      <c r="M9" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="N9" s="96" t="s">
-        <v>66</v>
-      </c>
-      <c r="O9" s="14"/>
-      <c r="P9" s="137"/>
-    </row>
-    <row r="10" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
+      <c r="D9" s="87"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="K9" s="89" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="M9" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="O9" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q9" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" s="12"/>
+      <c r="T9" s="125"/>
+    </row>
+    <row r="10" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="119" t="s">
+      <c r="B10" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="52">
         <v>0.08</v>
       </c>
-      <c r="D10" s="100"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="100">
+      <c r="D10" s="92"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="92">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H10" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="K10" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="M10" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="N10" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="O10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
+      <c r="H10" s="92">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I10" s="92">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J10" s="92">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="K10" s="92">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L10" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="O10" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="P10" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="R10" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="S10" s="12"/>
+    </row>
+    <row r="11" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="117" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="58">
-        <v>0</v>
-      </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" s="96" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" s="96" t="s">
-        <v>66</v>
-      </c>
-      <c r="K11" s="96" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" s="99" t="s">
-        <v>66</v>
-      </c>
-      <c r="M11" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="N11" s="96" t="s">
-        <v>66</v>
-      </c>
-      <c r="O11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
+      <c r="B11" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="53">
+        <v>0</v>
+      </c>
+      <c r="D11" s="90"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="L11" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="P11" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q11" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="R11" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="S11" s="12"/>
+    </row>
+    <row r="12" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="54">
+      <c r="B12" s="111" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="49">
         <v>-0.68</v>
       </c>
-      <c r="D12" s="100"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="127"/>
-      <c r="G12" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="K12" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="L12" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="N12" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="O12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="s">
+      <c r="D12" s="92"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="O12" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="P12" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q12" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="R12" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="S12" s="12"/>
+    </row>
+    <row r="13" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="119" t="s">
+      <c r="B13" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="54">
-        <v>0</v>
-      </c>
-      <c r="D13" s="100"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="I13" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="K13" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="M13" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="N13" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="O13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="16" t="s">
+      <c r="C13" s="49">
+        <v>0</v>
+      </c>
+      <c r="D13" s="92"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="O13" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="P13" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q13" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="R13" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="S13" s="12"/>
+    </row>
+    <row r="14" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="119" t="s">
+      <c r="B14" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="49">
         <v>1.18</v>
       </c>
-      <c r="D14" s="100"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="127"/>
-      <c r="G14" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="I14" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="J14" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="K14" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="L14" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="M14" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="N14" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="O14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18" t="s">
+      <c r="D14" s="92"/>
+      <c r="E14" s="93"/>
+      <c r="F14" s="93"/>
+      <c r="G14" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="K14" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="N14" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="O14" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="P14" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q14" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="R14" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="S14" s="12"/>
+    </row>
+    <row r="15" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="121" t="s">
+      <c r="B15" s="113" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="84">
+      <c r="C15" s="78">
         <v>0.04</v>
       </c>
-      <c r="D15" s="103">
+      <c r="D15" s="95">
         <v>0.1</v>
       </c>
-      <c r="E15" s="104">
+      <c r="E15" s="96">
         <v>0.01</v>
       </c>
-      <c r="F15" s="104">
+      <c r="F15" s="96">
         <v>0.04</v>
       </c>
-      <c r="G15" s="103">
+      <c r="G15" s="95">
         <v>0.08</v>
       </c>
-      <c r="H15" s="103">
-        <v>0</v>
-      </c>
-      <c r="I15" s="104">
+      <c r="H15" s="95">
+        <v>0.08</v>
+      </c>
+      <c r="I15" s="95">
+        <v>0.08</v>
+      </c>
+      <c r="J15" s="95">
+        <v>0.08</v>
+      </c>
+      <c r="K15" s="95">
+        <v>0.08</v>
+      </c>
+      <c r="L15" s="95">
+        <v>0</v>
+      </c>
+      <c r="M15" s="96">
         <v>0.05</v>
       </c>
-      <c r="J15" s="104">
+      <c r="N15" s="96">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K15" s="104">
+      <c r="O15" s="96">
         <v>0.09</v>
       </c>
-      <c r="L15" s="105">
+      <c r="P15" s="97">
         <v>0.1</v>
       </c>
-      <c r="M15" s="103">
+      <c r="Q15" s="95">
         <v>0.16</v>
       </c>
-      <c r="N15" s="104">
+      <c r="R15" s="96">
         <v>0.01</v>
       </c>
-      <c r="O15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
+      <c r="S15" s="12"/>
+    </row>
+    <row r="16" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="117" t="s">
+      <c r="B16" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C16" s="77">
+      <c r="C16" s="71">
         <v>-0.1</v>
       </c>
-      <c r="D16" s="106"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="106" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="106" t="s">
-        <v>66</v>
-      </c>
-      <c r="I16" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="J16" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="K16" s="108" t="s">
-        <v>66</v>
-      </c>
-      <c r="L16" s="107" t="s">
-        <v>66</v>
-      </c>
-      <c r="M16" s="106" t="s">
-        <v>66</v>
-      </c>
-      <c r="N16" s="107" t="s">
-        <v>66</v>
-      </c>
-      <c r="O16" s="67"/>
-    </row>
-    <row r="17" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="s">
+      <c r="D16" s="98"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="K16" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="N16" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="O16" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="P16" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q16" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="R16" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="S16" s="4"/>
+    </row>
+    <row r="17" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="119" t="s">
+      <c r="B17" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="78">
+      <c r="C17" s="72">
         <v>0.04</v>
       </c>
-      <c r="D17" s="109"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="110"/>
-      <c r="G17" s="109">
+      <c r="D17" s="101"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="101">
         <v>0.03</v>
       </c>
-      <c r="H17" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="K17" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="110" t="s">
-        <v>66</v>
-      </c>
-      <c r="M17" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="N17" s="110" t="s">
-        <v>66</v>
-      </c>
-      <c r="O17" s="67"/>
-    </row>
-    <row r="18" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
+      <c r="H17" s="101">
+        <v>0.03</v>
+      </c>
+      <c r="I17" s="101">
+        <v>0.03</v>
+      </c>
+      <c r="J17" s="101">
+        <v>0.03</v>
+      </c>
+      <c r="K17" s="101">
+        <v>0.03</v>
+      </c>
+      <c r="L17" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="N17" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="O17" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="P17" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q17" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="R17" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="S17" s="4"/>
+    </row>
+    <row r="18" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="119" t="s">
+      <c r="B18" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="85">
+      <c r="C18" s="79">
         <v>-0.16</v>
       </c>
-      <c r="D18" s="109"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="109">
+      <c r="D18" s="101"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="101">
         <v>-0.46</v>
       </c>
-      <c r="H18" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="I18" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="J18" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="K18" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="L18" s="110" t="s">
-        <v>66</v>
-      </c>
-      <c r="M18" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="N18" s="110" t="s">
-        <v>66</v>
-      </c>
-      <c r="O18" s="67"/>
-    </row>
-    <row r="19" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
+      <c r="H18" s="101">
+        <v>-0.46</v>
+      </c>
+      <c r="I18" s="101">
+        <v>-0.46</v>
+      </c>
+      <c r="J18" s="101">
+        <v>-0.46</v>
+      </c>
+      <c r="K18" s="101">
+        <v>-0.46</v>
+      </c>
+      <c r="L18" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="M18" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="N18" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="O18" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="P18" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q18" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="R18" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="S18" s="4"/>
+    </row>
+    <row r="19" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="78">
+      <c r="C19" s="72">
         <v>-0.02</v>
       </c>
-      <c r="D19" s="109"/>
-      <c r="E19" s="111"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="I19" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="K19" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="L19" s="110" t="s">
-        <v>66</v>
-      </c>
-      <c r="M19" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="N19" s="110" t="s">
-        <v>66</v>
-      </c>
-      <c r="O19" s="67"/>
-    </row>
-    <row r="20" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="68" t="s">
+      <c r="D19" s="101"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="K19" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="L19" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="N19" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="O19" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="P19" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q19" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="R19" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="S19" s="4"/>
+    </row>
+    <row r="20" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="122" t="s">
+      <c r="B20" s="114" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="79">
+      <c r="C20" s="73">
         <v>-0.36</v>
       </c>
-      <c r="D20" s="112"/>
-      <c r="E20" s="114"/>
-      <c r="F20" s="113"/>
-      <c r="G20" s="112" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="112" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="114" t="s">
-        <v>66</v>
-      </c>
-      <c r="J20" s="114" t="s">
-        <v>66</v>
-      </c>
-      <c r="K20" s="114" t="s">
-        <v>66</v>
-      </c>
-      <c r="L20" s="113" t="s">
-        <v>66</v>
-      </c>
-      <c r="M20" s="112" t="s">
-        <v>66</v>
-      </c>
-      <c r="N20" s="113" t="s">
-        <v>66</v>
-      </c>
-      <c r="O20" s="67"/>
-    </row>
-    <row r="21" spans="1:15" ht="3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="128"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="128"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="6"/>
-    </row>
-    <row r="22" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O22" s="6"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="L20" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="M20" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="N20" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="O20" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="P20" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q20" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="R20" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="S20" s="4"/>
+    </row>
+    <row r="21" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="4"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S22" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:N1"/>
-    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="B1:R1"/>
+    <mergeCell ref="T7:T9"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" scale="90" orientation="landscape" r:id="rId1"/>
@@ -2272,607 +2455,616 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Tabelle3"/>
-  <dimension ref="A1:AG10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AE10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" style="31" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" style="31" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="31" customWidth="1"/>
-    <col min="4" max="5" width="9.7109375" style="31" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="31" customWidth="1"/>
-    <col min="7" max="8" width="9.7109375" style="31" customWidth="1"/>
-    <col min="9" max="12" width="12.5703125" style="31" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="31" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="31" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" style="31" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="31" customWidth="1"/>
-    <col min="17" max="17" width="10.140625" style="31" customWidth="1"/>
-    <col min="18" max="18" width="11.42578125" style="31"/>
-    <col min="19" max="21" width="10.140625" style="31" customWidth="1"/>
-    <col min="22" max="25" width="12.5703125" style="31" customWidth="1"/>
-    <col min="26" max="27" width="10.140625" style="31" customWidth="1"/>
-    <col min="28" max="16384" width="11.42578125" style="31"/>
+    <col min="1" max="1" width="30.5" customWidth="1"/>
+    <col min="2" max="2" width="29.5" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="4" max="5" width="9.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="7" max="12" width="9.6640625" customWidth="1"/>
+    <col min="13" max="16" width="12.5" customWidth="1"/>
+    <col min="17" max="17" width="10.5" customWidth="1"/>
+    <col min="18" max="18" width="9.6640625" customWidth="1"/>
+    <col min="19" max="19" width="8.5" customWidth="1"/>
+    <col min="20" max="20" width="13.1640625" customWidth="1"/>
+    <col min="21" max="21" width="10.1640625" customWidth="1"/>
+    <col min="23" max="25" width="10.1640625" customWidth="1"/>
+    <col min="26" max="29" width="12.5" customWidth="1"/>
+    <col min="30" max="31" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="66" t="str">
+    <row r="1" spans="1:31" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="61" t="str">
         <f>ScoringParams!A1</f>
         <v>mobi31test</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="P1" s="7"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="AA1" s="1"/>
+      <c r="T1" s="5"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-    </row>
-    <row r="2" spans="1:33" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+    </row>
+    <row r="2" spans="1:31" s="25" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29" t="s">
+      <c r="T2" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" s="29"/>
-    </row>
-    <row r="3" spans="1:33" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+    </row>
+    <row r="3" spans="1:31" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="23" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="M3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="N3" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="O3" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="L3" s="24" t="s">
+      <c r="P3" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="Q3" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="R3" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="23" t="str">
+      <c r="T3" s="21" t="str">
         <f>C3</f>
         <v>global</v>
       </c>
-      <c r="Q3" s="23" t="str">
+      <c r="U3" s="21" t="str">
         <f>D3</f>
         <v>car</v>
       </c>
-      <c r="R3" s="24" t="str">
-        <f t="shared" ref="R3:AA3" si="0">E3</f>
+      <c r="V3" s="22" t="str">
+        <f>E3</f>
         <v>ride</v>
       </c>
-      <c r="S3" s="24" t="str">
-        <f t="shared" si="0"/>
+      <c r="W3" s="22" t="str">
+        <f>F3</f>
         <v>avtaxi</v>
       </c>
-      <c r="T3" s="24" t="str">
-        <f t="shared" si="0"/>
+      <c r="X3" s="22" t="str">
+        <f>G3</f>
         <v>pt</v>
       </c>
-      <c r="U3" s="24" t="str">
-        <f t="shared" si="0"/>
+      <c r="Y3" s="22" t="str">
+        <f t="shared" ref="Y3:AE3" si="0">L3</f>
         <v>walk</v>
       </c>
-      <c r="V3" s="24" t="str">
+      <c r="Z3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>car_feeder</v>
       </c>
-      <c r="W3" s="24" t="str">
+      <c r="AA3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ride_feeder</v>
       </c>
-      <c r="X3" s="24" t="str">
+      <c r="AB3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>bike_feeder</v>
       </c>
-      <c r="Y3" s="24" t="str">
+      <c r="AC3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>av_feeder</v>
       </c>
-      <c r="Z3" s="24" t="str">
+      <c r="AD3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>walk_main</v>
       </c>
-      <c r="AA3" s="25" t="str">
+      <c r="AE3" s="23" t="str">
         <f t="shared" si="0"/>
         <v>bike</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A4" s="43" t="s">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.15">
+      <c r="A4" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="35">
-        <v>0</v>
-      </c>
-      <c r="E4" s="33">
-        <v>0</v>
-      </c>
-      <c r="F4" s="33">
-        <v>0</v>
-      </c>
-      <c r="G4" s="33">
-        <v>0</v>
-      </c>
-      <c r="H4" s="33">
-        <v>0</v>
-      </c>
-      <c r="I4" s="33">
-        <v>0</v>
-      </c>
-      <c r="J4" s="33">
-        <v>0</v>
-      </c>
-      <c r="K4" s="33">
-        <v>0</v>
-      </c>
-      <c r="L4" s="33">
-        <v>0</v>
-      </c>
-      <c r="M4" s="33">
-        <v>0</v>
-      </c>
-      <c r="N4" s="36">
-        <v>0</v>
-      </c>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="62">
+      <c r="C4" s="64"/>
+      <c r="D4" s="30">
+        <v>0</v>
+      </c>
+      <c r="E4" s="28">
+        <v>0</v>
+      </c>
+      <c r="F4" s="28">
+        <v>0</v>
+      </c>
+      <c r="G4" s="28">
+        <v>0</v>
+      </c>
+      <c r="H4" s="28">
+        <v>0</v>
+      </c>
+      <c r="I4" s="28">
+        <v>0</v>
+      </c>
+      <c r="J4" s="28">
+        <v>0</v>
+      </c>
+      <c r="K4" s="28">
+        <v>0</v>
+      </c>
+      <c r="L4" s="28">
+        <v>0</v>
+      </c>
+      <c r="M4" s="28">
+        <v>0</v>
+      </c>
+      <c r="N4" s="28">
+        <v>0</v>
+      </c>
+      <c r="O4" s="28">
+        <v>0</v>
+      </c>
+      <c r="P4" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="28">
+        <v>0</v>
+      </c>
+      <c r="R4" s="31">
+        <v>0</v>
+      </c>
+      <c r="T4" s="65"/>
+      <c r="U4" s="57">
         <f>D4+ScoringParams!D4</f>
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="R4" s="63">
+      <c r="V4" s="58">
         <f>E4+ScoringParams!E4</f>
         <v>-0.7</v>
       </c>
-      <c r="S4" s="48">
+      <c r="W4" s="43">
         <f>F4+ScoringParams!F4</f>
         <v>0</v>
       </c>
-      <c r="T4" s="63">
+      <c r="X4" s="58">
         <f>G4+ScoringParams!G4</f>
         <v>-0.02</v>
       </c>
-      <c r="U4" s="63">
-        <f>H4+ScoringParams!H4</f>
-        <v>0</v>
-      </c>
-      <c r="V4" s="63">
-        <f>I4+ScoringParams!I4</f>
+      <c r="Y4" s="58">
+        <f>L4+ScoringParams!L4</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="58">
+        <f>M4+ScoringParams!M4</f>
         <v>-0.43</v>
       </c>
-      <c r="W4" s="63">
-        <f>J4+ScoringParams!J4</f>
+      <c r="AA4" s="58">
+        <f>N4+ScoringParams!N4</f>
         <v>-0.26</v>
       </c>
-      <c r="X4" s="48">
-        <f>K4+ScoringParams!K4</f>
+      <c r="AB4" s="43">
+        <f>O4+ScoringParams!O4</f>
         <v>-0.06</v>
       </c>
-      <c r="Y4" s="48">
-        <f>L4+ScoringParams!L4</f>
+      <c r="AC4" s="43">
+        <f>P4+ScoringParams!P4</f>
         <v>-0.17</v>
       </c>
-      <c r="Z4" s="48">
-        <f>M4+ScoringParams!M4</f>
+      <c r="AD4" s="43">
+        <f>Q4+ScoringParams!Q4</f>
         <v>0.02</v>
       </c>
-      <c r="AA4" s="49">
-        <f>N4+ScoringParams!N4</f>
+      <c r="AE4" s="44">
+        <f>R4+ScoringParams!R4</f>
         <v>-0.24</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.15">
+      <c r="A5" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="70"/>
-      <c r="D5" s="56">
+      <c r="C5" s="64"/>
+      <c r="D5" s="51">
         <v>-1.2E-5</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="50">
         <v>-3.3000000000000002E-6</v>
       </c>
-      <c r="F5" s="55">
-        <v>0</v>
-      </c>
-      <c r="G5" s="55">
+      <c r="F5" s="50">
+        <v>0</v>
+      </c>
+      <c r="G5" s="50">
         <v>1.5E-5</v>
       </c>
-      <c r="H5" s="33">
-        <v>0</v>
-      </c>
-      <c r="I5" s="55">
-        <v>0</v>
-      </c>
-      <c r="J5" s="55">
-        <v>0</v>
-      </c>
-      <c r="K5" s="55">
-        <v>0</v>
-      </c>
-      <c r="L5" s="55">
-        <v>0</v>
-      </c>
-      <c r="M5" s="33">
-        <v>0</v>
-      </c>
-      <c r="N5" s="36">
-        <v>0</v>
-      </c>
-      <c r="P5" s="75"/>
-      <c r="Q5" s="40">
+      <c r="H5" s="50">
+        <v>1.5E-5</v>
+      </c>
+      <c r="I5" s="50">
+        <v>1.5E-5</v>
+      </c>
+      <c r="J5" s="50">
+        <v>1.5E-5</v>
+      </c>
+      <c r="K5" s="50">
+        <v>1.5E-5</v>
+      </c>
+      <c r="L5" s="28">
+        <v>0</v>
+      </c>
+      <c r="M5" s="50">
+        <v>0</v>
+      </c>
+      <c r="N5" s="50">
+        <v>0</v>
+      </c>
+      <c r="O5" s="50">
+        <v>0</v>
+      </c>
+      <c r="P5" s="50">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="28">
+        <v>0</v>
+      </c>
+      <c r="R5" s="31">
+        <v>0</v>
+      </c>
+      <c r="T5" s="69"/>
+      <c r="U5" s="35">
         <f>D5+ScoringParams!D5</f>
         <v>-1.2E-5</v>
       </c>
-      <c r="R5" s="59">
+      <c r="V5" s="54">
         <f>E5+ScoringParams!E5</f>
         <v>-3.3000000000000002E-6</v>
       </c>
-      <c r="S5" s="50">
+      <c r="W5" s="45">
         <f>F5+ScoringParams!F5</f>
         <v>0</v>
       </c>
-      <c r="T5" s="59">
+      <c r="X5" s="54">
         <f>G5+ScoringParams!G5</f>
         <v>1.5E-5</v>
       </c>
-      <c r="U5" s="59">
-        <f>H5+ScoringParams!H5</f>
-        <v>0</v>
-      </c>
-      <c r="V5" s="59">
-        <f>I5+ScoringParams!I5</f>
-        <v>0</v>
-      </c>
-      <c r="W5" s="59">
-        <f>J5+ScoringParams!J5</f>
-        <v>0</v>
-      </c>
-      <c r="X5" s="50">
-        <f>K5+ScoringParams!K5</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="50">
+      <c r="Y5" s="54">
         <f>L5+ScoringParams!L5</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="50">
+      <c r="Z5" s="54">
         <f>M5+ScoringParams!M5</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="51">
+      <c r="AA5" s="54">
         <f>N5+ScoringParams!N5</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
+      <c r="AB5" s="45">
+        <f>O5+ScoringParams!O5</f>
+        <v>0</v>
+      </c>
+      <c r="AC5" s="45">
+        <f>P5+ScoringParams!P5</f>
+        <v>0</v>
+      </c>
+      <c r="AD5" s="45">
+        <f>Q5+ScoringParams!Q5</f>
+        <v>0</v>
+      </c>
+      <c r="AE5" s="46">
+        <f>R5+ScoringParams!R5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.15">
+      <c r="A6" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="70"/>
-      <c r="D6" s="35">
-        <v>0</v>
-      </c>
-      <c r="E6" s="33">
-        <v>0</v>
-      </c>
-      <c r="F6" s="33">
-        <v>0</v>
-      </c>
-      <c r="G6" s="33">
-        <v>0</v>
-      </c>
-      <c r="H6" s="33">
-        <v>0</v>
-      </c>
-      <c r="I6" s="33">
-        <v>0</v>
-      </c>
-      <c r="J6" s="33">
-        <v>0</v>
-      </c>
-      <c r="K6" s="33">
-        <v>0</v>
-      </c>
-      <c r="L6" s="33">
-        <v>0</v>
-      </c>
-      <c r="M6" s="33">
-        <v>0</v>
-      </c>
-      <c r="N6" s="36">
-        <v>0</v>
-      </c>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="42">
+      <c r="C6" s="64"/>
+      <c r="D6" s="30">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28">
+        <v>0</v>
+      </c>
+      <c r="I6" s="28">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28">
+        <v>0</v>
+      </c>
+      <c r="L6" s="28">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28">
+        <v>0</v>
+      </c>
+      <c r="N6" s="28">
+        <v>0</v>
+      </c>
+      <c r="O6" s="28">
+        <v>0</v>
+      </c>
+      <c r="P6" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="28">
+        <v>0</v>
+      </c>
+      <c r="R6" s="31">
+        <v>0</v>
+      </c>
+      <c r="T6" s="69"/>
+      <c r="U6" s="37">
         <f>D6+ScoringParams!D6</f>
         <v>-0.44</v>
       </c>
-      <c r="R6" s="41">
+      <c r="V6" s="36">
         <f>E6+ScoringParams!E6</f>
         <v>-0.79</v>
       </c>
-      <c r="S6" s="50">
+      <c r="W6" s="45">
         <f>F6+ScoringParams!F6</f>
         <v>-0.17</v>
       </c>
-      <c r="T6" s="41">
+      <c r="X6" s="36">
         <f>G6+ScoringParams!G6</f>
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="U6" s="41">
-        <f>H6+ScoringParams!H6</f>
+      <c r="Y6" s="36">
+        <f>L6+ScoringParams!L6</f>
         <v>-0.31</v>
       </c>
-      <c r="V6" s="41">
-        <f>I6+ScoringParams!I6</f>
+      <c r="Z6" s="36">
+        <f>M6+ScoringParams!M6</f>
         <v>-0.22</v>
       </c>
-      <c r="W6" s="41">
-        <f>J6+ScoringParams!J6</f>
+      <c r="AA6" s="36">
+        <f>N6+ScoringParams!N6</f>
         <v>-0.09</v>
       </c>
-      <c r="X6" s="50">
-        <f>K6+ScoringParams!K6</f>
+      <c r="AB6" s="45">
+        <f>O6+ScoringParams!O6</f>
         <v>-0.57999999999999996</v>
       </c>
-      <c r="Y6" s="50">
-        <f>L6+ScoringParams!L6</f>
+      <c r="AC6" s="45">
+        <f>P6+ScoringParams!P6</f>
         <v>-3.25</v>
       </c>
-      <c r="Z6" s="50">
-        <f>M6+ScoringParams!M6</f>
+      <c r="AD6" s="45">
+        <f>Q6+ScoringParams!Q6</f>
         <v>-0.05</v>
       </c>
-      <c r="AA6" s="51">
-        <f>N6+ScoringParams!N6</f>
+      <c r="AE6" s="46">
+        <f>R6+ScoringParams!R6</f>
         <v>-0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A7" s="44" t="s">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.15">
+      <c r="A7" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="70"/>
-      <c r="D7" s="37">
+      <c r="C7" s="64"/>
+      <c r="D7" s="32">
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="29">
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="F7" s="34">
-        <v>0</v>
-      </c>
-      <c r="G7" s="34">
+      <c r="F7" s="29">
+        <v>0</v>
+      </c>
+      <c r="G7" s="29">
         <v>-3.4200000000000002E-4</v>
       </c>
-      <c r="H7" s="34">
-        <v>0</v>
-      </c>
-      <c r="I7" s="34">
+      <c r="H7" s="29">
+        <v>-3.4200000000000002E-4</v>
+      </c>
+      <c r="I7" s="29">
+        <v>-3.4200000000000002E-4</v>
+      </c>
+      <c r="J7" s="29">
+        <v>-3.4200000000000002E-4</v>
+      </c>
+      <c r="K7" s="29">
+        <v>-3.4200000000000002E-4</v>
+      </c>
+      <c r="L7" s="29">
+        <v>0</v>
+      </c>
+      <c r="M7" s="29">
         <f>D7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="J7" s="34">
+      <c r="N7" s="29">
         <f>E7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="K7" s="34">
-        <v>0</v>
-      </c>
-      <c r="L7" s="34">
-        <v>0</v>
-      </c>
-      <c r="M7" s="34">
-        <v>0</v>
-      </c>
-      <c r="N7" s="38">
-        <v>0</v>
-      </c>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="60">
+      <c r="O7" s="29">
+        <v>0</v>
+      </c>
+      <c r="P7" s="29">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="29">
+        <v>0</v>
+      </c>
+      <c r="R7" s="33">
+        <v>0</v>
+      </c>
+      <c r="T7" s="66"/>
+      <c r="U7" s="55">
         <f>D7+ScoringParams!D7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="R7" s="61">
+      <c r="V7" s="56">
         <f>E7+ScoringParams!E7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="S7" s="46">
+      <c r="W7" s="41">
         <f>F7+ScoringParams!F7</f>
         <v>0</v>
       </c>
-      <c r="T7" s="61">
+      <c r="X7" s="56">
         <f>G7+ScoringParams!G7</f>
         <v>-3.4200000000000002E-4</v>
       </c>
-      <c r="U7" s="61">
-        <f>H7+ScoringParams!H7</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="61">
-        <f>I7+ScoringParams!I7</f>
+      <c r="Y7" s="56">
+        <f>L7+ScoringParams!L7</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="56">
+        <f>M7+ScoringParams!M7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="W7" s="61">
-        <f>J7+ScoringParams!J7</f>
+      <c r="AA7" s="56">
+        <f>N7+ScoringParams!N7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="X7" s="46">
-        <f>K7+ScoringParams!K7</f>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="46">
-        <f>L7+ScoringParams!L7</f>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="46">
-        <f>M7+ScoringParams!M7</f>
-        <v>0</v>
-      </c>
-      <c r="AA7" s="47">
-        <f>N7+ScoringParams!N7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A8" s="43" t="s">
+      <c r="AB7" s="41">
+        <f>O7+ScoringParams!O7</f>
+        <v>0</v>
+      </c>
+      <c r="AC7" s="41">
+        <f>P7+ScoringParams!P7</f>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="41">
+        <f>Q7+ScoringParams!Q7</f>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="42">
+        <f>R7+ScoringParams!R7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.15">
+      <c r="A8" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="73">
-        <v>0</v>
-      </c>
-      <c r="P8" s="81">
+      <c r="C8" s="67">
+        <v>0</v>
+      </c>
+      <c r="T8" s="75">
         <f>C8+ScoringParams!C16</f>
         <v>-0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A9" s="44" t="s">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.15">
+      <c r="A9" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="76">
-        <v>0</v>
-      </c>
-      <c r="P9" s="82">
+      <c r="C9" s="70">
+        <v>0</v>
+      </c>
+      <c r="T9" s="76">
         <f>C9+ScoringParams!C17</f>
         <v>0.04</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A10" s="45" t="s">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.15">
+      <c r="A10" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="68" t="s">
+      <c r="B10" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="74">
-        <v>0</v>
-      </c>
-      <c r="P10" s="83">
+      <c r="C10" s="68">
+        <v>0</v>
+      </c>
+      <c r="T10" s="77">
         <f>C10+ScoringParams!C18</f>
         <v>-0.16</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D4:G7 M4:N7">
-    <cfRule type="cellIs" dxfId="10" priority="27" operator="notEqual">
+  <conditionalFormatting sqref="C8:C10">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:G7 M4:N7">
-    <cfRule type="cellIs" dxfId="9" priority="26" operator="equal">
+  <conditionalFormatting sqref="D4:R7">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8:P10 Q4:R7 T4:Y7">
-    <cfRule type="cellIs" dxfId="8" priority="14" operator="between">
+  <conditionalFormatting sqref="T8:T10">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="between">
       <formula>0</formula>
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:C10">
-    <cfRule type="cellIs" dxfId="7" priority="11" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8:C10">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:L4 H6:L7 H5">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:L4 H6:L7 H5">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:L5">
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I5:L5">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z4:AA7">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="between">
-      <formula>0</formula>
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S4:S7">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="between">
+  <conditionalFormatting sqref="U4:AE7">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>0</formula>
       <formula>0</formula>
     </cfRule>

--- a/test/input/scenarios/mobi50test/scoringParametersIT.xlsx
+++ b/test/input/scenarios/mobi50test/scoringParametersIT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annevaleriepreto/Documents/EPFL/matsim-sbb/test/input/scenarios/mobi50test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\devsbb\code\matsim-sbb\test\input\scenarios\mobi50test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BCDBFA-4C7D-6845-94DC-91F300C98923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F23F66E-61AB-43A3-B71C-2D75BB4A02EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="900" windowWidth="29080" windowHeight="18060" tabRatio="674" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="674" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScoringParams" sheetId="25" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="72">
   <si>
     <t>adaptation time</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>other</t>
+  </si>
+  <si>
+    <t>non_network_walk</t>
   </si>
 </sst>
 </file>
@@ -935,7 +938,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1352,31 +1355,31 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:Y22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
     <col min="4" max="6" width="10" customWidth="1"/>
-    <col min="7" max="11" width="11.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" customWidth="1"/>
-    <col min="13" max="16" width="12.5" customWidth="1"/>
-    <col min="17" max="17" width="10.33203125" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" customWidth="1"/>
-    <col min="19" max="19" width="5.5" style="2" customWidth="1"/>
-    <col min="20" max="20" width="33.6640625" customWidth="1"/>
-    <col min="23" max="23" width="24.5" style="1" customWidth="1"/>
-    <col min="24" max="24" width="8.5" style="1" customWidth="1"/>
-    <col min="26" max="28" width="7.83203125" customWidth="1"/>
-    <col min="29" max="29" width="7.33203125" customWidth="1"/>
-    <col min="30" max="30" width="7.83203125" customWidth="1"/>
-    <col min="31" max="31" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="7.83203125" customWidth="1"/>
-    <col min="35" max="35" width="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="11.28515625" customWidth="1"/>
+    <col min="12" max="13" width="12.140625" customWidth="1"/>
+    <col min="14" max="17" width="12.42578125" customWidth="1"/>
+    <col min="18" max="18" width="10.28515625" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" customWidth="1"/>
+    <col min="20" max="20" width="5.42578125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="33.7109375" customWidth="1"/>
+    <col min="24" max="24" width="24.42578125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="8.42578125" style="1" customWidth="1"/>
+    <col min="27" max="29" width="7.85546875" customWidth="1"/>
+    <col min="30" max="30" width="7.28515625" customWidth="1"/>
+    <col min="31" max="31" width="7.85546875" customWidth="1"/>
+    <col min="32" max="32" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="7.85546875" customWidth="1"/>
+    <col min="36" max="36" width="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="59" t="s">
         <v>64</v>
       </c>
@@ -1399,9 +1402,10 @@
       <c r="P1" s="123"/>
       <c r="Q1" s="123"/>
       <c r="R1" s="123"/>
-      <c r="S1" s="5"/>
+      <c r="S1" s="123"/>
+      <c r="T1" s="5"/>
     </row>
-    <row r="2" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
         <v>31</v>
       </c>
@@ -1436,27 +1440,30 @@
       <c r="L2" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="M2" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="N2" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="N2" s="22" t="s">
+      <c r="O2" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="O2" s="22" t="s">
+      <c r="P2" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="P2" s="23" t="s">
+      <c r="Q2" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="R2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="S2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
     </row>
-    <row r="3" spans="1:20" ht="50.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="50.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17"/>
       <c r="B3" s="107" t="s">
         <v>15</v>
@@ -1491,30 +1498,33 @@
       <c r="L3" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="116" t="s">
+      <c r="M3" s="115" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="N3" s="116" t="s">
+      <c r="O3" s="116" t="s">
         <v>56</v>
       </c>
-      <c r="O3" s="116" t="s">
+      <c r="P3" s="116" t="s">
         <v>57</v>
       </c>
-      <c r="P3" s="108" t="s">
+      <c r="Q3" s="108" t="s">
         <v>62</v>
       </c>
-      <c r="Q3" s="115" t="s">
+      <c r="R3" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="R3" s="108" t="s">
+      <c r="S3" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="11"/>
-      <c r="T3" s="18" t="s">
+      <c r="T3" s="11"/>
+      <c r="U3" s="18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
@@ -1549,30 +1559,33 @@
       <c r="L4" s="84">
         <v>0</v>
       </c>
-      <c r="M4" s="120">
+      <c r="M4" s="84">
+        <v>0</v>
+      </c>
+      <c r="N4" s="120">
         <v>-0.43</v>
       </c>
-      <c r="N4" s="85">
+      <c r="O4" s="85">
         <v>-0.26</v>
       </c>
-      <c r="O4" s="85">
+      <c r="P4" s="85">
         <v>-0.06</v>
       </c>
-      <c r="P4" s="86">
+      <c r="Q4" s="86">
         <v>-0.17</v>
       </c>
-      <c r="Q4" s="84">
+      <c r="R4" s="84">
         <v>0.02</v>
       </c>
-      <c r="R4" s="86">
+      <c r="S4" s="86">
         <v>-0.24</v>
       </c>
-      <c r="S4" s="12"/>
-      <c r="T4" s="19" t="s">
+      <c r="T4" s="12"/>
+      <c r="U4" s="19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:21" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
@@ -1607,7 +1620,7 @@
       <c r="L5" s="81">
         <v>0</v>
       </c>
-      <c r="M5" s="82">
+      <c r="M5" s="81">
         <v>0</v>
       </c>
       <c r="N5" s="82">
@@ -1616,21 +1629,24 @@
       <c r="O5" s="82">
         <v>0</v>
       </c>
-      <c r="P5" s="83">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="81">
-        <v>0</v>
-      </c>
-      <c r="R5" s="82">
-        <v>0</v>
-      </c>
-      <c r="S5" s="12"/>
-      <c r="T5" s="20" t="s">
+      <c r="P5" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="83">
+        <v>0</v>
+      </c>
+      <c r="R5" s="81">
+        <v>0</v>
+      </c>
+      <c r="S5" s="82">
+        <v>0</v>
+      </c>
+      <c r="T5" s="12"/>
+      <c r="U5" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
         <v>13</v>
       </c>
@@ -1665,30 +1681,33 @@
       <c r="L6" s="47">
         <v>-0.31</v>
       </c>
-      <c r="M6" s="48">
+      <c r="M6" s="47">
+        <v>-0.31</v>
+      </c>
+      <c r="N6" s="48">
         <v>-0.22</v>
       </c>
-      <c r="N6" s="48">
+      <c r="O6" s="48">
         <v>-0.09</v>
       </c>
-      <c r="O6" s="48">
+      <c r="P6" s="48">
         <v>-0.57999999999999996</v>
       </c>
-      <c r="P6" s="80">
+      <c r="Q6" s="80">
         <v>-3.25</v>
       </c>
-      <c r="Q6" s="47">
+      <c r="R6" s="47">
         <v>-0.05</v>
       </c>
-      <c r="R6" s="48">
+      <c r="S6" s="48">
         <v>-0.7</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="63" t="s">
+      <c r="T6" s="13"/>
+      <c r="U6" s="63" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>12</v>
       </c>
@@ -1723,7 +1742,7 @@
       <c r="L7" s="81">
         <v>0</v>
       </c>
-      <c r="M7" s="82">
+      <c r="M7" s="81">
         <v>0</v>
       </c>
       <c r="N7" s="82">
@@ -1732,21 +1751,24 @@
       <c r="O7" s="82">
         <v>0</v>
       </c>
-      <c r="P7" s="83">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="81">
-        <v>0</v>
-      </c>
-      <c r="R7" s="82">
-        <v>0</v>
-      </c>
-      <c r="S7" s="11"/>
-      <c r="T7" s="124" t="s">
+      <c r="P7" s="82">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="83">
+        <v>0</v>
+      </c>
+      <c r="R7" s="81">
+        <v>0</v>
+      </c>
+      <c r="S7" s="82">
+        <v>0</v>
+      </c>
+      <c r="T7" s="11"/>
+      <c r="U7" s="124" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="0.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:21" ht="0.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14"/>
       <c r="B8" s="111"/>
       <c r="C8" s="34"/>
@@ -1775,7 +1797,7 @@
       <c r="L8" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="M8" s="37" t="s">
         <v>66</v>
       </c>
       <c r="N8" s="34" t="s">
@@ -1784,19 +1806,22 @@
       <c r="O8" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="P8" s="118" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q8" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="R8" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="S8" s="11"/>
-      <c r="T8" s="124"/>
+      <c r="P8" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q8" s="118" t="s">
+        <v>66</v>
+      </c>
+      <c r="R8" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="S8" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="T8" s="11"/>
+      <c r="U8" s="124"/>
     </row>
-    <row r="9" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>11</v>
       </c>
@@ -1827,7 +1852,7 @@
       <c r="L9" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="M9" s="88" t="s">
+      <c r="M9" s="90" t="s">
         <v>66</v>
       </c>
       <c r="N9" s="88" t="s">
@@ -1836,19 +1861,22 @@
       <c r="O9" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="91" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q9" s="90" t="s">
-        <v>66</v>
-      </c>
-      <c r="R9" s="88" t="s">
-        <v>66</v>
-      </c>
-      <c r="S9" s="12"/>
-      <c r="T9" s="125"/>
+      <c r="P9" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q9" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="T9" s="12"/>
+      <c r="U9" s="125"/>
     </row>
-    <row r="10" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>10</v>
       </c>
@@ -1879,7 +1907,7 @@
       <c r="L10" s="92" t="s">
         <v>66</v>
       </c>
-      <c r="M10" s="93" t="s">
+      <c r="M10" s="92" t="s">
         <v>66</v>
       </c>
       <c r="N10" s="93" t="s">
@@ -1888,18 +1916,21 @@
       <c r="O10" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="P10" s="94" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q10" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="R10" s="93" t="s">
-        <v>66</v>
-      </c>
-      <c r="S10" s="12"/>
+      <c r="P10" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="R10" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="S10" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="T10" s="12"/>
     </row>
-    <row r="11" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
         <v>9</v>
       </c>
@@ -1930,7 +1961,7 @@
       <c r="L11" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="M11" s="88" t="s">
+      <c r="M11" s="90" t="s">
         <v>66</v>
       </c>
       <c r="N11" s="88" t="s">
@@ -1939,18 +1970,21 @@
       <c r="O11" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="P11" s="91" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q11" s="90" t="s">
-        <v>66</v>
-      </c>
-      <c r="R11" s="88" t="s">
-        <v>66</v>
-      </c>
-      <c r="S11" s="12"/>
+      <c r="P11" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q11" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="R11" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="S11" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" s="12"/>
     </row>
-    <row r="12" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
         <v>8</v>
       </c>
@@ -1981,7 +2015,7 @@
       <c r="L12" s="92" t="s">
         <v>66</v>
       </c>
-      <c r="M12" s="93" t="s">
+      <c r="M12" s="92" t="s">
         <v>66</v>
       </c>
       <c r="N12" s="93" t="s">
@@ -1990,18 +2024,21 @@
       <c r="O12" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="P12" s="94" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q12" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="R12" s="93" t="s">
-        <v>66</v>
-      </c>
-      <c r="S12" s="12"/>
+      <c r="P12" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q12" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="R12" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="S12" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="T12" s="12"/>
     </row>
-    <row r="13" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>7</v>
       </c>
@@ -2032,7 +2069,7 @@
       <c r="L13" s="92" t="s">
         <v>66</v>
       </c>
-      <c r="M13" s="93" t="s">
+      <c r="M13" s="92" t="s">
         <v>66</v>
       </c>
       <c r="N13" s="93" t="s">
@@ -2041,18 +2078,21 @@
       <c r="O13" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="P13" s="94" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q13" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="R13" s="93" t="s">
-        <v>66</v>
-      </c>
-      <c r="S13" s="12"/>
+      <c r="P13" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q13" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="R13" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="S13" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="T13" s="12"/>
     </row>
-    <row r="14" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>6</v>
       </c>
@@ -2083,7 +2123,7 @@
       <c r="L14" s="92" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="93" t="s">
+      <c r="M14" s="92" t="s">
         <v>66</v>
       </c>
       <c r="N14" s="93" t="s">
@@ -2092,18 +2132,21 @@
       <c r="O14" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="P14" s="94" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q14" s="92" t="s">
-        <v>66</v>
-      </c>
-      <c r="R14" s="93" t="s">
-        <v>66</v>
-      </c>
-      <c r="S14" s="12"/>
+      <c r="P14" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q14" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="R14" s="92" t="s">
+        <v>66</v>
+      </c>
+      <c r="S14" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="T14" s="12"/>
     </row>
-    <row r="15" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>4</v>
       </c>
@@ -2140,27 +2183,30 @@
       <c r="L15" s="95">
         <v>0</v>
       </c>
-      <c r="M15" s="96">
+      <c r="M15" s="95">
+        <v>0</v>
+      </c>
+      <c r="N15" s="96">
         <v>0.05</v>
       </c>
-      <c r="N15" s="96">
+      <c r="O15" s="96">
         <v>0.14000000000000001</v>
       </c>
-      <c r="O15" s="96">
+      <c r="P15" s="96">
         <v>0.09</v>
       </c>
-      <c r="P15" s="97">
+      <c r="Q15" s="97">
         <v>0.1</v>
       </c>
-      <c r="Q15" s="95">
+      <c r="R15" s="95">
         <v>0.16</v>
       </c>
-      <c r="R15" s="96">
+      <c r="S15" s="96">
         <v>0.01</v>
       </c>
-      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
     </row>
-    <row r="16" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>41</v>
       </c>
@@ -2191,7 +2237,7 @@
       <c r="L16" s="98" t="s">
         <v>66</v>
       </c>
-      <c r="M16" s="100" t="s">
+      <c r="M16" s="98" t="s">
         <v>66</v>
       </c>
       <c r="N16" s="100" t="s">
@@ -2200,18 +2246,21 @@
       <c r="O16" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="P16" s="99" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q16" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="R16" s="99" t="s">
-        <v>66</v>
-      </c>
-      <c r="S16" s="4"/>
+      <c r="P16" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q16" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="R16" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="S16" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="T16" s="4"/>
     </row>
-    <row r="17" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>47</v>
       </c>
@@ -2242,7 +2291,7 @@
       <c r="L17" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="M17" s="103" t="s">
+      <c r="M17" s="101" t="s">
         <v>66</v>
       </c>
       <c r="N17" s="103" t="s">
@@ -2251,18 +2300,21 @@
       <c r="O17" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q17" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="R17" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="S17" s="4"/>
+      <c r="P17" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q17" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="R17" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="S17" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="T17" s="4"/>
     </row>
-    <row r="18" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
         <v>43</v>
       </c>
@@ -2293,7 +2345,7 @@
       <c r="L18" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="M18" s="103" t="s">
+      <c r="M18" s="101" t="s">
         <v>66</v>
       </c>
       <c r="N18" s="103" t="s">
@@ -2302,18 +2354,21 @@
       <c r="O18" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="P18" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q18" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="R18" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="S18" s="4"/>
+      <c r="P18" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q18" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="R18" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="S18" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="T18" s="4"/>
     </row>
-    <row r="19" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
         <v>48</v>
       </c>
@@ -2344,7 +2399,7 @@
       <c r="L19" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="M19" s="103" t="s">
+      <c r="M19" s="101" t="s">
         <v>66</v>
       </c>
       <c r="N19" s="103" t="s">
@@ -2353,18 +2408,21 @@
       <c r="O19" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="P19" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q19" s="101" t="s">
-        <v>66</v>
-      </c>
-      <c r="R19" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="S19" s="4"/>
+      <c r="P19" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q19" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="R19" s="101" t="s">
+        <v>66</v>
+      </c>
+      <c r="S19" s="102" t="s">
+        <v>66</v>
+      </c>
+      <c r="T19" s="4"/>
     </row>
-    <row r="20" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="62" t="s">
         <v>49</v>
       </c>
@@ -2395,7 +2453,7 @@
       <c r="L20" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="M20" s="106" t="s">
+      <c r="M20" s="104" t="s">
         <v>66</v>
       </c>
       <c r="N20" s="106" t="s">
@@ -2404,18 +2462,21 @@
       <c r="O20" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="P20" s="105" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q20" s="104" t="s">
-        <v>66</v>
-      </c>
-      <c r="R20" s="105" t="s">
-        <v>66</v>
-      </c>
-      <c r="S20" s="4"/>
+      <c r="P20" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q20" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="R20" s="104" t="s">
+        <v>66</v>
+      </c>
+      <c r="S20" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="T20" s="4"/>
     </row>
-    <row r="21" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:20" ht="3" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="6"/>
@@ -2432,17 +2493,18 @@
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
       <c r="P21" s="7"/>
-      <c r="Q21" s="6"/>
+      <c r="Q21" s="7"/>
       <c r="R21" s="6"/>
-      <c r="S21" s="4"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="4"/>
     </row>
-    <row r="22" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="S22" s="4"/>
+    <row r="22" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T22" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:R1"/>
-    <mergeCell ref="T7:T9"/>
+    <mergeCell ref="B1:S1"/>
+    <mergeCell ref="U7:U9"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" scale="90" orientation="landscape" r:id="rId1"/>
@@ -2455,47 +2517,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Tabelle3"/>
-  <dimension ref="A1:AE10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:AF10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.5" customWidth="1"/>
-    <col min="2" max="2" width="29.5" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" customWidth="1"/>
-    <col min="4" max="5" width="9.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" customWidth="1"/>
-    <col min="7" max="12" width="9.6640625" customWidth="1"/>
-    <col min="13" max="16" width="12.5" customWidth="1"/>
-    <col min="17" max="17" width="10.5" customWidth="1"/>
-    <col min="18" max="18" width="9.6640625" customWidth="1"/>
-    <col min="19" max="19" width="8.5" customWidth="1"/>
-    <col min="20" max="20" width="13.1640625" customWidth="1"/>
-    <col min="21" max="21" width="10.1640625" customWidth="1"/>
-    <col min="23" max="25" width="10.1640625" customWidth="1"/>
-    <col min="26" max="29" width="12.5" customWidth="1"/>
-    <col min="30" max="31" width="10.1640625" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" customWidth="1"/>
+    <col min="7" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="17" width="12.42578125" customWidth="1"/>
+    <col min="18" max="18" width="10.42578125" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="20" max="20" width="8.42578125" customWidth="1"/>
+    <col min="21" max="21" width="13.140625" customWidth="1"/>
+    <col min="22" max="22" width="10.140625" customWidth="1"/>
+    <col min="24" max="26" width="10.140625" customWidth="1"/>
+    <col min="27" max="30" width="12.42578125" customWidth="1"/>
+    <col min="31" max="32" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="50.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:32" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="61" t="str">
         <f>ScoringParams!A1</f>
         <v>mobi31test</v>
       </c>
-      <c r="T1" s="5"/>
-      <c r="AB1" s="1"/>
+      <c r="U1" s="5"/>
       <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
     </row>
-    <row r="2" spans="1:31" s="25" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" s="25" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="60" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="T2" s="25" t="s">
+      <c r="U2" s="25" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:32" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="26" t="s">
         <v>36</v>
       </c>
@@ -2531,73 +2593,76 @@
         <v>26</v>
       </c>
       <c r="M3" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="N3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="O3" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="22" t="s">
+      <c r="P3" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="22" t="s">
+      <c r="Q3" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="Q3" s="22" t="s">
+      <c r="R3" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="R3" s="23" t="s">
+      <c r="S3" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="T3" s="21" t="str">
+      <c r="U3" s="21" t="str">
         <f>C3</f>
         <v>global</v>
       </c>
-      <c r="U3" s="21" t="str">
+      <c r="V3" s="21" t="str">
         <f>D3</f>
         <v>car</v>
       </c>
-      <c r="V3" s="22" t="str">
+      <c r="W3" s="22" t="str">
         <f>E3</f>
         <v>ride</v>
       </c>
-      <c r="W3" s="22" t="str">
+      <c r="X3" s="22" t="str">
         <f>F3</f>
         <v>avtaxi</v>
       </c>
-      <c r="X3" s="22" t="str">
+      <c r="Y3" s="22" t="str">
         <f>G3</f>
         <v>pt</v>
       </c>
-      <c r="Y3" s="22" t="str">
-        <f t="shared" ref="Y3:AE3" si="0">L3</f>
-        <v>walk</v>
-      </c>
       <c r="Z3" s="22" t="str">
+        <f t="shared" ref="Z3:AF3" si="0">M3</f>
+        <v>non_network_walk</v>
+      </c>
+      <c r="AA3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>car_feeder</v>
       </c>
-      <c r="AA3" s="22" t="str">
+      <c r="AB3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>ride_feeder</v>
       </c>
-      <c r="AB3" s="22" t="str">
+      <c r="AC3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>bike_feeder</v>
       </c>
-      <c r="AC3" s="22" t="str">
+      <c r="AD3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>av_feeder</v>
       </c>
-      <c r="AD3" s="22" t="str">
+      <c r="AE3" s="22" t="str">
         <f t="shared" si="0"/>
         <v>walk_main</v>
       </c>
-      <c r="AE3" s="23" t="str">
+      <c r="AF3" s="23" t="str">
         <f t="shared" si="0"/>
         <v>bike</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="38" t="s">
         <v>37</v>
       </c>
@@ -2647,56 +2712,59 @@
       <c r="Q4" s="28">
         <v>0</v>
       </c>
-      <c r="R4" s="31">
-        <v>0</v>
-      </c>
-      <c r="T4" s="65"/>
-      <c r="U4" s="57">
+      <c r="R4" s="28">
+        <v>0</v>
+      </c>
+      <c r="S4" s="31">
+        <v>0</v>
+      </c>
+      <c r="U4" s="65"/>
+      <c r="V4" s="57">
         <f>D4+ScoringParams!D4</f>
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="V4" s="58">
+      <c r="W4" s="58">
         <f>E4+ScoringParams!E4</f>
         <v>-0.7</v>
       </c>
-      <c r="W4" s="43">
+      <c r="X4" s="43">
         <f>F4+ScoringParams!F4</f>
         <v>0</v>
       </c>
-      <c r="X4" s="58">
+      <c r="Y4" s="58">
         <f>G4+ScoringParams!G4</f>
         <v>-0.02</v>
       </c>
-      <c r="Y4" s="58">
-        <f>L4+ScoringParams!L4</f>
-        <v>0</v>
-      </c>
       <c r="Z4" s="58">
-        <f>M4+ScoringParams!M4</f>
-        <v>-0.43</v>
+        <f>M4+ScoringParams!L4</f>
+        <v>0</v>
       </c>
       <c r="AA4" s="58">
         <f>N4+ScoringParams!N4</f>
+        <v>-0.43</v>
+      </c>
+      <c r="AB4" s="58">
+        <f>O4+ScoringParams!O4</f>
         <v>-0.26</v>
-      </c>
-      <c r="AB4" s="43">
-        <f>O4+ScoringParams!O4</f>
-        <v>-0.06</v>
       </c>
       <c r="AC4" s="43">
         <f>P4+ScoringParams!P4</f>
-        <v>-0.17</v>
+        <v>-0.06</v>
       </c>
       <c r="AD4" s="43">
         <f>Q4+ScoringParams!Q4</f>
+        <v>-0.17</v>
+      </c>
+      <c r="AE4" s="43">
+        <f>R4+ScoringParams!R4</f>
         <v>0.02</v>
       </c>
-      <c r="AE4" s="44">
-        <f>R4+ScoringParams!R4</f>
+      <c r="AF4" s="44">
+        <f>S4+ScoringParams!S4</f>
         <v>-0.24</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
         <v>37</v>
       </c>
@@ -2731,7 +2799,7 @@
       <c r="L5" s="28">
         <v>0</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="28">
         <v>0</v>
       </c>
       <c r="N5" s="50">
@@ -2743,42 +2811,41 @@
       <c r="P5" s="50">
         <v>0</v>
       </c>
-      <c r="Q5" s="28">
-        <v>0</v>
-      </c>
-      <c r="R5" s="31">
-        <v>0</v>
-      </c>
-      <c r="T5" s="69"/>
-      <c r="U5" s="35">
+      <c r="Q5" s="50">
+        <v>0</v>
+      </c>
+      <c r="R5" s="28">
+        <v>0</v>
+      </c>
+      <c r="S5" s="31">
+        <v>0</v>
+      </c>
+      <c r="U5" s="69"/>
+      <c r="V5" s="35">
         <f>D5+ScoringParams!D5</f>
         <v>-1.2E-5</v>
       </c>
-      <c r="V5" s="54">
+      <c r="W5" s="54">
         <f>E5+ScoringParams!E5</f>
         <v>-3.3000000000000002E-6</v>
       </c>
-      <c r="W5" s="45">
+      <c r="X5" s="45">
         <f>F5+ScoringParams!F5</f>
         <v>0</v>
       </c>
-      <c r="X5" s="54">
+      <c r="Y5" s="54">
         <f>G5+ScoringParams!G5</f>
         <v>1.5E-5</v>
       </c>
-      <c r="Y5" s="54">
-        <f>L5+ScoringParams!L5</f>
-        <v>0</v>
-      </c>
       <c r="Z5" s="54">
-        <f>M5+ScoringParams!M5</f>
+        <f>M5+ScoringParams!L5</f>
         <v>0</v>
       </c>
       <c r="AA5" s="54">
         <f>N5+ScoringParams!N5</f>
         <v>0</v>
       </c>
-      <c r="AB5" s="45">
+      <c r="AB5" s="54">
         <f>O5+ScoringParams!O5</f>
         <v>0</v>
       </c>
@@ -2790,12 +2857,16 @@
         <f>Q5+ScoringParams!Q5</f>
         <v>0</v>
       </c>
-      <c r="AE5" s="46">
+      <c r="AE5" s="45">
         <f>R5+ScoringParams!R5</f>
         <v>0</v>
       </c>
+      <c r="AF5" s="46">
+        <f>S5+ScoringParams!S5</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="39" t="s">
         <v>37</v>
       </c>
@@ -2845,56 +2916,59 @@
       <c r="Q6" s="28">
         <v>0</v>
       </c>
-      <c r="R6" s="31">
-        <v>0</v>
-      </c>
-      <c r="T6" s="69"/>
-      <c r="U6" s="37">
+      <c r="R6" s="28">
+        <v>0</v>
+      </c>
+      <c r="S6" s="31">
+        <v>0</v>
+      </c>
+      <c r="U6" s="69"/>
+      <c r="V6" s="37">
         <f>D6+ScoringParams!D6</f>
         <v>-0.44</v>
       </c>
-      <c r="V6" s="36">
+      <c r="W6" s="36">
         <f>E6+ScoringParams!E6</f>
         <v>-0.79</v>
       </c>
-      <c r="W6" s="45">
+      <c r="X6" s="45">
         <f>F6+ScoringParams!F6</f>
         <v>-0.17</v>
       </c>
-      <c r="X6" s="36">
+      <c r="Y6" s="36">
         <f>G6+ScoringParams!G6</f>
         <v>-7.0000000000000007E-2</v>
       </c>
-      <c r="Y6" s="36">
-        <f>L6+ScoringParams!L6</f>
+      <c r="Z6" s="36">
+        <f>M6+ScoringParams!L6</f>
         <v>-0.31</v>
-      </c>
-      <c r="Z6" s="36">
-        <f>M6+ScoringParams!M6</f>
-        <v>-0.22</v>
       </c>
       <c r="AA6" s="36">
         <f>N6+ScoringParams!N6</f>
+        <v>-0.22</v>
+      </c>
+      <c r="AB6" s="36">
+        <f>O6+ScoringParams!O6</f>
         <v>-0.09</v>
-      </c>
-      <c r="AB6" s="45">
-        <f>O6+ScoringParams!O6</f>
-        <v>-0.57999999999999996</v>
       </c>
       <c r="AC6" s="45">
         <f>P6+ScoringParams!P6</f>
-        <v>-3.25</v>
+        <v>-0.57999999999999996</v>
       </c>
       <c r="AD6" s="45">
         <f>Q6+ScoringParams!Q6</f>
+        <v>-3.25</v>
+      </c>
+      <c r="AE6" s="45">
+        <f>R6+ScoringParams!R6</f>
         <v>-0.05</v>
       </c>
-      <c r="AE6" s="46">
-        <f>R6+ScoringParams!R6</f>
+      <c r="AF6" s="46">
+        <f>S6+ScoringParams!S6</f>
         <v>-0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" s="39" t="s">
         <v>37</v>
       </c>
@@ -2930,57 +3004,56 @@
         <v>0</v>
       </c>
       <c r="M7" s="29">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>D7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="N7" s="29">
+      <c r="O7" s="29">
         <f>E7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="O7" s="29">
-        <v>0</v>
-      </c>
       <c r="P7" s="29">
         <v>0</v>
       </c>
       <c r="Q7" s="29">
         <v>0</v>
       </c>
-      <c r="R7" s="33">
-        <v>0</v>
-      </c>
-      <c r="T7" s="66"/>
-      <c r="U7" s="55">
+      <c r="R7" s="29">
+        <v>0</v>
+      </c>
+      <c r="S7" s="33">
+        <v>0</v>
+      </c>
+      <c r="U7" s="66"/>
+      <c r="V7" s="55">
         <f>D7+ScoringParams!D7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="V7" s="56">
+      <c r="W7" s="56">
         <f>E7+ScoringParams!E7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="W7" s="41">
+      <c r="X7" s="41">
         <f>F7+ScoringParams!F7</f>
         <v>0</v>
       </c>
-      <c r="X7" s="56">
+      <c r="Y7" s="56">
         <f>G7+ScoringParams!G7</f>
         <v>-3.4200000000000002E-4</v>
       </c>
-      <c r="Y7" s="56">
-        <f>L7+ScoringParams!L7</f>
-        <v>0</v>
-      </c>
       <c r="Z7" s="56">
-        <f>M7+ScoringParams!M7</f>
-        <v>-2.1800000000000001E-4</v>
+        <f>M7+ScoringParams!L7</f>
+        <v>0</v>
       </c>
       <c r="AA7" s="56">
         <f>N7+ScoringParams!N7</f>
         <v>-2.1800000000000001E-4</v>
       </c>
-      <c r="AB7" s="41">
+      <c r="AB7" s="56">
         <f>O7+ScoringParams!O7</f>
-        <v>0</v>
+        <v>-2.1800000000000001E-4</v>
       </c>
       <c r="AC7" s="41">
         <f>P7+ScoringParams!P7</f>
@@ -2990,12 +3063,16 @@
         <f>Q7+ScoringParams!Q7</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="42">
+      <c r="AE7" s="41">
         <f>R7+ScoringParams!R7</f>
         <v>0</v>
       </c>
+      <c r="AF7" s="42">
+        <f>S7+ScoringParams!S7</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
         <v>37</v>
       </c>
@@ -3005,12 +3082,12 @@
       <c r="C8" s="67">
         <v>0</v>
       </c>
-      <c r="T8" s="75">
+      <c r="U8" s="75">
         <f>C8+ScoringParams!C16</f>
         <v>-0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" s="39" t="s">
         <v>37</v>
       </c>
@@ -3020,12 +3097,12 @@
       <c r="C9" s="70">
         <v>0</v>
       </c>
-      <c r="T9" s="76">
+      <c r="U9" s="76">
         <f>C9+ScoringParams!C17</f>
         <v>0.04</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" s="40" t="s">
         <v>37</v>
       </c>
@@ -3035,7 +3112,7 @@
       <c r="C10" s="68">
         <v>0</v>
       </c>
-      <c r="T10" s="77">
+      <c r="U10" s="77">
         <f>C10+ScoringParams!C18</f>
         <v>-0.16</v>
       </c>
@@ -3049,7 +3126,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:R7">
+  <conditionalFormatting sqref="D4:S7">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
@@ -3057,13 +3134,13 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T8:T10">
+  <conditionalFormatting sqref="U8:U10">
     <cfRule type="cellIs" dxfId="1" priority="14" operator="between">
       <formula>0</formula>
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:AE7">
+  <conditionalFormatting sqref="V4:AF7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>0</formula>
       <formula>0</formula>
